--- a/ex_res_2_after_fix.xlsx
+++ b/ex_res_2_after_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\DataStructuresHW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FA0EF2-A9A8-4AE1-AF74-1BD4A8AFD246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5777242-3E3B-495F-9801-1973EF3B6447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,13 +37,13 @@
     <t>run_time</t>
   </si>
   <si>
+    <t>amount_of_search_time (original)</t>
+  </si>
+  <si>
+    <t>total amount of search time</t>
+  </si>
+  <si>
     <t>run_time (seconds)</t>
-  </si>
-  <si>
-    <t>amount_of_search_time (original)</t>
-  </si>
-  <si>
-    <t>total amount of search time</t>
   </si>
 </sst>
 </file>
@@ -385,15 +385,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.8984375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -409,16 +400,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -442,11 +433,11 @@
         <v>7353</v>
       </c>
       <c r="G2">
-        <v>3.686000127345324E-3</v>
+        <v>3.1264499993994832E-3</v>
       </c>
       <c r="H2">
         <f>G2*1000</f>
-        <v>3.686000127345324</v>
+        <v>3.1264499993994832</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -470,11 +461,11 @@
         <v>15927</v>
       </c>
       <c r="G3">
-        <v>1.1046800063923E-2</v>
+        <v>7.1755250028218143E-3</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H11" si="1">G3*1000</f>
-        <v>11.046800063923</v>
+        <v>7.1755250028218143</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -498,11 +489,11 @@
         <v>34277</v>
       </c>
       <c r="G4">
-        <v>1.7627699999138709E-2</v>
+        <v>1.6613824998785279E-2</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>17.627699999138709</v>
+        <v>16.61382499878528</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -526,11 +517,11 @@
         <v>73379</v>
       </c>
       <c r="G5">
-        <v>3.6831900011748082E-2</v>
+        <v>3.2179075002204627E-2</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>36.831900011748083</v>
+        <v>32.179075002204627</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -554,11 +545,11 @@
         <v>156385</v>
       </c>
       <c r="G6">
-        <v>9.4366499921306968E-2</v>
+        <v>6.3417049997951835E-2</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>94.366499921306968</v>
+        <v>63.417049997951835</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -582,11 +573,11 @@
         <v>331999</v>
       </c>
       <c r="G7">
-        <v>0.14677430014126</v>
+        <v>0.14745174999552549</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>146.77430014126</v>
+        <v>147.45174999552549</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -610,11 +601,11 @@
         <v>702429</v>
       </c>
       <c r="G8">
-        <v>0.27984640002250671</v>
+        <v>0.33342612500564428</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>279.84640002250671</v>
+        <v>333.42612500564428</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -638,11 +629,11 @@
         <v>1481691</v>
       </c>
       <c r="G9">
-        <v>1.527183199999854</v>
+        <v>0.58894132501154672</v>
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>1527.183199999854</v>
+        <v>588.94132501154672</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -666,11 +657,11 @@
         <v>3117017</v>
       </c>
       <c r="G10">
-        <v>2.6217982999514788</v>
+        <v>1.2006973250099691</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>2621.7982999514788</v>
+        <v>1200.6973250099691</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -694,11 +685,11 @@
         <v>6541271</v>
       </c>
       <c r="G11">
-        <v>2.5939563999418169</v>
+        <v>3.369722700001148</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>2593.9563999418169</v>
+        <v>3369.722700001148</v>
       </c>
     </row>
   </sheetData>
